--- a/게임구상.xlsx
+++ b/게임구상.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRO\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRO\Desktop\GitDesktop\Power-Clicker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8783B8D7-764B-4FC0-B365-D99E1D1B34D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB993C7-F015-49AB-9792-C7A00CDA797E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-3165" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="RPG세계" sheetId="34" r:id="rId1"/>
-    <sheet name="시스템" sheetId="25" r:id="rId2"/>
-    <sheet name="지도" sheetId="28" r:id="rId3"/>
+    <sheet name="우주" sheetId="35" r:id="rId1"/>
+    <sheet name="RPG세계" sheetId="34" r:id="rId2"/>
+    <sheet name="시스템" sheetId="25" r:id="rId3"/>
+    <sheet name="지도" sheetId="28" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="874">
   <si>
     <t>농장</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4257,6 +4258,110 @@
   </si>
   <si>
     <t>대상 가문 관계+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 우주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>준지성체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고대시대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>원시시대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중세시대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우주시대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현대시대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기술</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>은하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>행성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대륙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 문명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하이브</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포유류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도시 개척</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>절대왕정, 신학</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업화, 사회개혁, 대륙이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTL문명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건물명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>직업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>의사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경찰서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경찰</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5014,7 +5119,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="261">
+  <cellXfs count="263">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5498,12 +5603,249 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="20" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5531,54 +5873,18 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="40" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5588,215 +5894,20 @@
     <xf numFmtId="0" fontId="40" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="20" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -17207,6 +17318,175 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4CD2896-FD18-45EB-B2DB-DFDAED004973}">
+  <dimension ref="A1:S16"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>848</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>860</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="162" t="s">
+        <v>855</v>
+      </c>
+      <c r="B2" t="s">
+        <v>856</v>
+      </c>
+      <c r="J2" s="162" t="s">
+        <v>855</v>
+      </c>
+      <c r="K2" t="s">
+        <v>853</v>
+      </c>
+      <c r="L2" t="s">
+        <v>868</v>
+      </c>
+      <c r="R2" t="s">
+        <v>869</v>
+      </c>
+      <c r="S2" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="162"/>
+      <c r="B3" t="s">
+        <v>858</v>
+      </c>
+      <c r="J3" s="162"/>
+      <c r="K3" t="s">
+        <v>854</v>
+      </c>
+      <c r="L3" t="s">
+        <v>867</v>
+      </c>
+      <c r="R3" t="s">
+        <v>588</v>
+      </c>
+      <c r="S3" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" s="162"/>
+      <c r="B4" t="s">
+        <v>857</v>
+      </c>
+      <c r="J4" s="162"/>
+      <c r="K4" t="s">
+        <v>852</v>
+      </c>
+      <c r="L4" t="s">
+        <v>866</v>
+      </c>
+      <c r="R4" t="s">
+        <v>872</v>
+      </c>
+      <c r="S4" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="162"/>
+      <c r="B5" t="s">
+        <v>859</v>
+      </c>
+      <c r="J5" s="162"/>
+      <c r="K5" t="s">
+        <v>850</v>
+      </c>
+      <c r="L5" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" s="162"/>
+      <c r="B6" s="161" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="161"/>
+      <c r="J6" s="162"/>
+      <c r="K6" t="s">
+        <v>851</v>
+      </c>
+      <c r="L6" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" s="262"/>
+      <c r="B7" s="161"/>
+      <c r="C7" s="161"/>
+      <c r="J7" s="162" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" s="262"/>
+      <c r="B8" s="161"/>
+      <c r="C8" s="161"/>
+      <c r="J8" s="162"/>
+      <c r="K8" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="J9" s="162"/>
+      <c r="K9" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="J10" s="162"/>
+      <c r="K10" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="J11" s="162"/>
+      <c r="K11" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="J12" s="161"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="J13" s="161"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="J14" s="161"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="J15" s="161"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="J16" s="161"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="J2:J6"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="J7:J11"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98E035A0-C60F-418D-AF1F-E1502BFCA3E8}">
   <dimension ref="A1:Y34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -17223,7 +17503,7 @@
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A2" s="161" t="s">
+      <c r="A2" s="162" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
@@ -17232,7 +17512,7 @@
       <c r="C2" t="s">
         <v>639</v>
       </c>
-      <c r="I2" s="161" t="s">
+      <c r="I2" s="162" t="s">
         <v>12</v>
       </c>
       <c r="J2" t="s">
@@ -17244,7 +17524,7 @@
       <c r="L2" t="s">
         <v>808</v>
       </c>
-      <c r="R2" s="161" t="s">
+      <c r="R2" s="162" t="s">
         <v>600</v>
       </c>
       <c r="S2" t="s">
@@ -17267,7 +17547,7 @@
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A3" s="161"/>
+      <c r="A3" s="162"/>
       <c r="B3" s="156" t="s">
         <v>636</v>
       </c>
@@ -17277,7 +17557,7 @@
       <c r="E3" s="77" t="s">
         <v>663</v>
       </c>
-      <c r="I3" s="161"/>
+      <c r="I3" s="162"/>
       <c r="J3" t="s">
         <v>298</v>
       </c>
@@ -17287,7 +17567,7 @@
       <c r="L3" t="s">
         <v>747</v>
       </c>
-      <c r="R3" s="161"/>
+      <c r="R3" s="162"/>
       <c r="S3" t="s">
         <v>646</v>
       </c>
@@ -17299,7 +17579,7 @@
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A4" s="161"/>
+      <c r="A4" s="162"/>
       <c r="B4" s="157" t="s">
         <v>637</v>
       </c>
@@ -17309,7 +17589,7 @@
       <c r="E4" s="77" t="s">
         <v>640</v>
       </c>
-      <c r="I4" s="161"/>
+      <c r="I4" s="162"/>
       <c r="J4" t="s">
         <v>693</v>
       </c>
@@ -17319,7 +17599,7 @@
       <c r="L4" t="s">
         <v>815</v>
       </c>
-      <c r="R4" s="161"/>
+      <c r="R4" s="162"/>
       <c r="S4" t="s">
         <v>191</v>
       </c>
@@ -17331,7 +17611,7 @@
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A5" s="161"/>
+      <c r="A5" s="162"/>
       <c r="B5" s="157" t="s">
         <v>638</v>
       </c>
@@ -17341,7 +17621,7 @@
       <c r="E5" s="77" t="s">
         <v>664</v>
       </c>
-      <c r="I5" s="161"/>
+      <c r="I5" s="162"/>
       <c r="J5" t="s">
         <v>586</v>
       </c>
@@ -17351,7 +17631,7 @@
       <c r="L5" t="s">
         <v>746</v>
       </c>
-      <c r="R5" s="161"/>
+      <c r="R5" s="162"/>
       <c r="S5" t="s">
         <v>695</v>
       </c>
@@ -17363,7 +17643,7 @@
       </c>
     </row>
     <row r="6" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="162" t="s">
+      <c r="A6" s="163" t="s">
         <v>828</v>
       </c>
       <c r="B6" t="s">
@@ -17375,7 +17655,7 @@
       <c r="D6" t="s">
         <v>754</v>
       </c>
-      <c r="I6" s="162" t="s">
+      <c r="I6" s="163" t="s">
         <v>757</v>
       </c>
       <c r="J6" t="s">
@@ -17393,7 +17673,7 @@
       <c r="O6" t="s">
         <v>833</v>
       </c>
-      <c r="R6" s="161" t="s">
+      <c r="R6" s="162" t="s">
         <v>599</v>
       </c>
       <c r="S6" t="s">
@@ -17407,7 +17687,7 @@
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A7" s="161"/>
+      <c r="A7" s="162"/>
       <c r="B7" t="s">
         <v>788</v>
       </c>
@@ -17417,7 +17697,7 @@
       <c r="D7" t="s">
         <v>755</v>
       </c>
-      <c r="I7" s="162"/>
+      <c r="I7" s="163"/>
       <c r="J7" t="s">
         <v>589</v>
       </c>
@@ -17433,7 +17713,7 @@
       <c r="O7" t="s">
         <v>831</v>
       </c>
-      <c r="R7" s="161"/>
+      <c r="R7" s="162"/>
       <c r="S7" t="s">
         <v>647</v>
       </c>
@@ -17445,7 +17725,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A8" s="161"/>
+      <c r="A8" s="162"/>
       <c r="B8" t="s">
         <v>753</v>
       </c>
@@ -17455,7 +17735,7 @@
       <c r="D8" t="s">
         <v>795</v>
       </c>
-      <c r="I8" s="162"/>
+      <c r="I8" s="163"/>
       <c r="J8" t="s">
         <v>588</v>
       </c>
@@ -17471,7 +17751,7 @@
       <c r="O8" t="s">
         <v>830</v>
       </c>
-      <c r="R8" s="161"/>
+      <c r="R8" s="162"/>
       <c r="S8" t="s">
         <v>182</v>
       </c>
@@ -17486,7 +17766,7 @@
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A9" s="161"/>
+      <c r="A9" s="162"/>
       <c r="B9" t="s">
         <v>752</v>
       </c>
@@ -17496,7 +17776,7 @@
       <c r="D9" t="s">
         <v>758</v>
       </c>
-      <c r="I9" s="162"/>
+      <c r="I9" s="163"/>
       <c r="J9" t="s">
         <v>620</v>
       </c>
@@ -17512,7 +17792,7 @@
       <c r="O9" t="s">
         <v>847</v>
       </c>
-      <c r="R9" s="161"/>
+      <c r="R9" s="162"/>
       <c r="S9" t="s">
         <v>648</v>
       </c>
@@ -17524,7 +17804,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="161" t="s">
+      <c r="A10" s="162" t="s">
         <v>623</v>
       </c>
       <c r="B10" t="s">
@@ -17539,7 +17819,7 @@
       <c r="E10">
         <v>-10</v>
       </c>
-      <c r="I10" s="162" t="s">
+      <c r="I10" s="163" t="s">
         <v>835</v>
       </c>
       <c r="J10" t="s">
@@ -17563,7 +17843,7 @@
       <c r="P10" s="82" t="s">
         <v>733</v>
       </c>
-      <c r="R10" s="162" t="s">
+      <c r="R10" s="163" t="s">
         <v>685</v>
       </c>
       <c r="S10" t="s">
@@ -17574,7 +17854,7 @@
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A11" s="161"/>
+      <c r="A11" s="162"/>
       <c r="B11" t="s">
         <v>625</v>
       </c>
@@ -17587,7 +17867,7 @@
       <c r="E11">
         <v>-5</v>
       </c>
-      <c r="I11" s="161"/>
+      <c r="I11" s="162"/>
       <c r="J11" t="s">
         <v>5</v>
       </c>
@@ -17609,7 +17889,7 @@
       <c r="P11" s="82" t="s">
         <v>734</v>
       </c>
-      <c r="R11" s="161"/>
+      <c r="R11" s="162"/>
       <c r="S11" t="s">
         <v>673</v>
       </c>
@@ -17618,7 +17898,7 @@
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A12" s="161"/>
+      <c r="A12" s="162"/>
       <c r="B12" t="s">
         <v>630</v>
       </c>
@@ -17631,7 +17911,7 @@
       <c r="E12">
         <v>-5</v>
       </c>
-      <c r="I12" s="161"/>
+      <c r="I12" s="162"/>
       <c r="J12" t="s">
         <v>45</v>
       </c>
@@ -17653,7 +17933,7 @@
       <c r="P12" s="82" t="s">
         <v>735</v>
       </c>
-      <c r="R12" s="161"/>
+      <c r="R12" s="162"/>
       <c r="S12" t="s">
         <v>824</v>
       </c>
@@ -17662,7 +17942,7 @@
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A13" s="161"/>
+      <c r="A13" s="162"/>
       <c r="B13" t="s">
         <v>628</v>
       </c>
@@ -17675,7 +17955,7 @@
       <c r="E13">
         <v>-1</v>
       </c>
-      <c r="I13" s="161"/>
+      <c r="I13" s="162"/>
       <c r="J13" t="s">
         <v>52</v>
       </c>
@@ -17697,7 +17977,7 @@
       <c r="P13" s="82" t="s">
         <v>736</v>
       </c>
-      <c r="R13" s="161"/>
+      <c r="R13" s="162"/>
       <c r="S13" t="s">
         <v>621</v>
       </c>
@@ -17709,7 +17989,7 @@
       </c>
     </row>
     <row r="14" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="161" t="s">
+      <c r="A14" s="162" t="s">
         <v>659</v>
       </c>
       <c r="B14" t="s">
@@ -17718,7 +17998,7 @@
       <c r="C14" s="156" t="s">
         <v>675</v>
       </c>
-      <c r="I14" s="161" t="s">
+      <c r="I14" s="162" t="s">
         <v>591</v>
       </c>
       <c r="J14" t="s">
@@ -17730,7 +18010,7 @@
       <c r="L14" t="s">
         <v>6</v>
       </c>
-      <c r="R14" s="162" t="s">
+      <c r="R14" s="163" t="s">
         <v>824</v>
       </c>
       <c r="S14" t="s">
@@ -17747,14 +18027,14 @@
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A15" s="161"/>
+      <c r="A15" s="162"/>
       <c r="B15" t="s">
         <v>551</v>
       </c>
       <c r="C15" t="s">
         <v>684</v>
       </c>
-      <c r="I15" s="161"/>
+      <c r="I15" s="162"/>
       <c r="J15" t="s">
         <v>1</v>
       </c>
@@ -17764,7 +18044,7 @@
       <c r="L15" t="s">
         <v>14</v>
       </c>
-      <c r="R15" s="161"/>
+      <c r="R15" s="162"/>
       <c r="S15" t="s">
         <v>704</v>
       </c>
@@ -17779,14 +18059,14 @@
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A16" s="161"/>
+      <c r="A16" s="162"/>
       <c r="B16" t="s">
         <v>634</v>
       </c>
       <c r="C16" t="s">
         <v>676</v>
       </c>
-      <c r="I16" s="161"/>
+      <c r="I16" s="162"/>
       <c r="J16" t="s">
         <v>43</v>
       </c>
@@ -17796,7 +18076,7 @@
       <c r="L16" t="s">
         <v>44</v>
       </c>
-      <c r="R16" s="161"/>
+      <c r="R16" s="162"/>
       <c r="S16" t="s">
         <v>703</v>
       </c>
@@ -17808,7 +18088,7 @@
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A17" s="161"/>
+      <c r="A17" s="162"/>
       <c r="B17" t="s">
         <v>516</v>
       </c>
@@ -17818,7 +18098,7 @@
       <c r="F17" s="157" t="s">
         <v>837</v>
       </c>
-      <c r="I17" s="161"/>
+      <c r="I17" s="162"/>
       <c r="J17" t="s">
         <v>55</v>
       </c>
@@ -17828,7 +18108,7 @@
       <c r="L17" t="s">
         <v>56</v>
       </c>
-      <c r="R17" s="161"/>
+      <c r="R17" s="162"/>
       <c r="S17" t="s">
         <v>797</v>
       </c>
@@ -17851,7 +18131,7 @@
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A19" s="161" t="s">
+      <c r="A19" s="162" t="s">
         <v>649</v>
       </c>
       <c r="B19" t="s">
@@ -17860,7 +18140,7 @@
       <c r="C19" t="s">
         <v>760</v>
       </c>
-      <c r="I19" s="161" t="s">
+      <c r="I19" s="162" t="s">
         <v>667</v>
       </c>
       <c r="J19" t="s">
@@ -17872,7 +18152,7 @@
       <c r="L19" t="s">
         <v>836</v>
       </c>
-      <c r="R19" s="161" t="s">
+      <c r="R19" s="162" t="s">
         <v>595</v>
       </c>
       <c r="S19" s="77" t="s">
@@ -17889,14 +18169,14 @@
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A20" s="161"/>
+      <c r="A20" s="162"/>
       <c r="B20" t="s">
         <v>323</v>
       </c>
       <c r="C20" t="s">
         <v>760</v>
       </c>
-      <c r="I20" s="161"/>
+      <c r="I20" s="162"/>
       <c r="J20" t="s">
         <v>168</v>
       </c>
@@ -17909,7 +18189,7 @@
       <c r="O20" t="s">
         <v>680</v>
       </c>
-      <c r="R20" s="161"/>
+      <c r="R20" s="162"/>
       <c r="S20" t="s">
         <v>31</v>
       </c>
@@ -17927,7 +18207,7 @@
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A21" s="161"/>
+      <c r="A21" s="162"/>
       <c r="B21" t="s">
         <v>325</v>
       </c>
@@ -17937,7 +18217,7 @@
       <c r="D21" t="s">
         <v>806</v>
       </c>
-      <c r="I21" s="161"/>
+      <c r="I21" s="162"/>
       <c r="J21" t="s">
         <v>186</v>
       </c>
@@ -17947,7 +18227,7 @@
       <c r="L21" t="s">
         <v>764</v>
       </c>
-      <c r="R21" s="161"/>
+      <c r="R21" s="162"/>
       <c r="S21" t="s">
         <v>212</v>
       </c>
@@ -17965,7 +18245,7 @@
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A22" s="161"/>
+      <c r="A22" s="162"/>
       <c r="B22" t="s">
         <v>414</v>
       </c>
@@ -17978,7 +18258,7 @@
       <c r="G22" t="s">
         <v>761</v>
       </c>
-      <c r="I22" s="161"/>
+      <c r="I22" s="162"/>
       <c r="J22" t="s">
         <v>167</v>
       </c>
@@ -17991,7 +18271,7 @@
       <c r="N22" t="s">
         <v>657</v>
       </c>
-      <c r="R22" s="161"/>
+      <c r="R22" s="162"/>
       <c r="S22" t="s">
         <v>817</v>
       </c>
@@ -18009,7 +18289,7 @@
       </c>
     </row>
     <row r="23" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="161" t="s">
+      <c r="A23" s="162" t="s">
         <v>591</v>
       </c>
       <c r="B23" t="s">
@@ -18018,7 +18298,7 @@
       <c r="C23" t="s">
         <v>617</v>
       </c>
-      <c r="I23" s="161" t="s">
+      <c r="I23" s="162" t="s">
         <v>668</v>
       </c>
       <c r="J23" t="s">
@@ -18034,7 +18314,7 @@
       <c r="P23" s="157" t="s">
         <v>837</v>
       </c>
-      <c r="R23" s="161" t="s">
+      <c r="R23" s="162" t="s">
         <v>596</v>
       </c>
       <c r="S23" t="s">
@@ -18045,14 +18325,14 @@
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A24" s="161"/>
+      <c r="A24" s="162"/>
       <c r="B24" t="s">
         <v>14</v>
       </c>
       <c r="C24" t="s">
         <v>617</v>
       </c>
-      <c r="I24" s="161"/>
+      <c r="I24" s="162"/>
       <c r="J24" t="s">
         <v>213</v>
       </c>
@@ -18066,7 +18346,7 @@
       <c r="P24" s="157" t="s">
         <v>837</v>
       </c>
-      <c r="R24" s="161"/>
+      <c r="R24" s="162"/>
       <c r="S24" t="s">
         <v>810</v>
       </c>
@@ -18075,14 +18355,14 @@
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A25" s="161"/>
+      <c r="A25" s="162"/>
       <c r="B25" t="s">
         <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>617</v>
       </c>
-      <c r="I25" s="161"/>
+      <c r="I25" s="162"/>
       <c r="J25" t="s">
         <v>187</v>
       </c>
@@ -18096,7 +18376,7 @@
       <c r="P25" s="157" t="s">
         <v>837</v>
       </c>
-      <c r="R25" s="161"/>
+      <c r="R25" s="162"/>
       <c r="S25" t="s">
         <v>608</v>
       </c>
@@ -18105,14 +18385,14 @@
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A26" s="161"/>
+      <c r="A26" s="162"/>
       <c r="B26" t="s">
         <v>56</v>
       </c>
       <c r="C26" t="s">
         <v>617</v>
       </c>
-      <c r="I26" s="161"/>
+      <c r="I26" s="162"/>
       <c r="J26" t="s">
         <v>67</v>
       </c>
@@ -18125,7 +18405,7 @@
       <c r="P26" s="157" t="s">
         <v>837</v>
       </c>
-      <c r="R26" s="161"/>
+      <c r="R26" s="162"/>
       <c r="S26" t="s">
         <v>783</v>
       </c>
@@ -18137,7 +18417,7 @@
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A27" s="161" t="s">
+      <c r="A27" s="162" t="s">
         <v>590</v>
       </c>
       <c r="B27" s="82" t="s">
@@ -18152,7 +18432,7 @@
       <c r="G27" t="s">
         <v>698</v>
       </c>
-      <c r="I27" s="162" t="s">
+      <c r="I27" s="163" t="s">
         <v>674</v>
       </c>
       <c r="J27" t="s">
@@ -18164,7 +18444,7 @@
       <c r="O27" t="s">
         <v>689</v>
       </c>
-      <c r="R27" s="161" t="s">
+      <c r="R27" s="162" t="s">
         <v>597</v>
       </c>
       <c r="S27" t="s">
@@ -18175,7 +18455,7 @@
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A28" s="161"/>
+      <c r="A28" s="162"/>
       <c r="B28" s="160" t="s">
         <v>803</v>
       </c>
@@ -18188,7 +18468,7 @@
       <c r="G28" t="s">
         <v>698</v>
       </c>
-      <c r="I28" s="161"/>
+      <c r="I28" s="162"/>
       <c r="J28" t="s">
         <v>658</v>
       </c>
@@ -18198,7 +18478,7 @@
       <c r="O28" t="s">
         <v>745</v>
       </c>
-      <c r="R28" s="161"/>
+      <c r="R28" s="162"/>
       <c r="S28" t="s">
         <v>741</v>
       </c>
@@ -18207,14 +18487,14 @@
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A29" s="161"/>
+      <c r="A29" s="162"/>
       <c r="B29" s="160" t="s">
         <v>804</v>
       </c>
       <c r="C29" t="s">
         <v>702</v>
       </c>
-      <c r="I29" s="161"/>
+      <c r="I29" s="162"/>
       <c r="J29" t="s">
         <v>642</v>
       </c>
@@ -18224,7 +18504,7 @@
       <c r="M29" t="s">
         <v>657</v>
       </c>
-      <c r="R29" s="161"/>
+      <c r="R29" s="162"/>
       <c r="S29" t="s">
         <v>781</v>
       </c>
@@ -18233,7 +18513,7 @@
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A30" s="161"/>
+      <c r="A30" s="162"/>
       <c r="B30" s="160" t="s">
         <v>805</v>
       </c>
@@ -18243,14 +18523,14 @@
       <c r="D30" t="s">
         <v>732</v>
       </c>
-      <c r="I30" s="161"/>
+      <c r="I30" s="162"/>
       <c r="J30" t="s">
         <v>759</v>
       </c>
       <c r="K30" t="s">
         <v>660</v>
       </c>
-      <c r="R30" s="161"/>
+      <c r="R30" s="162"/>
       <c r="S30" t="s">
         <v>744</v>
       </c>
@@ -18259,7 +18539,7 @@
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A31" s="162" t="s">
+      <c r="A31" s="163" t="s">
         <v>651</v>
       </c>
       <c r="B31" t="s">
@@ -18274,7 +18554,7 @@
       <c r="E31" t="s">
         <v>820</v>
       </c>
-      <c r="I31" s="161" t="s">
+      <c r="I31" s="162" t="s">
         <v>643</v>
       </c>
       <c r="J31" t="s">
@@ -18283,7 +18563,7 @@
       <c r="K31" t="s">
         <v>653</v>
       </c>
-      <c r="R31" s="161" t="s">
+      <c r="R31" s="162" t="s">
         <v>598</v>
       </c>
       <c r="S31" t="s">
@@ -18306,7 +18586,7 @@
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A32" s="161"/>
+      <c r="A32" s="162"/>
       <c r="B32" t="s">
         <v>725</v>
       </c>
@@ -18319,7 +18599,7 @@
       <c r="E32" t="s">
         <v>821</v>
       </c>
-      <c r="I32" s="161"/>
+      <c r="I32" s="162"/>
       <c r="J32" t="s">
         <v>654</v>
       </c>
@@ -18329,7 +18609,7 @@
       <c r="N32" t="s">
         <v>713</v>
       </c>
-      <c r="R32" s="161"/>
+      <c r="R32" s="162"/>
       <c r="S32" t="s">
         <v>602</v>
       </c>
@@ -18350,7 +18630,7 @@
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A33" s="161"/>
+      <c r="A33" s="162"/>
       <c r="B33" t="s">
         <v>724</v>
       </c>
@@ -18363,14 +18643,14 @@
       <c r="E33" t="s">
         <v>822</v>
       </c>
-      <c r="I33" s="161"/>
+      <c r="I33" s="162"/>
       <c r="J33" t="s">
         <v>714</v>
       </c>
       <c r="K33" t="s">
         <v>671</v>
       </c>
-      <c r="R33" s="161"/>
+      <c r="R33" s="162"/>
       <c r="S33" t="s">
         <v>603</v>
       </c>
@@ -18391,7 +18671,7 @@
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A34" s="161"/>
+      <c r="A34" s="162"/>
       <c r="B34" t="s">
         <v>730</v>
       </c>
@@ -18404,7 +18684,7 @@
       <c r="E34" t="s">
         <v>823</v>
       </c>
-      <c r="I34" s="161"/>
+      <c r="I34" s="162"/>
       <c r="J34" t="s">
         <v>651</v>
       </c>
@@ -18414,7 +18694,7 @@
       <c r="N34" t="s">
         <v>652</v>
       </c>
-      <c r="R34" s="161"/>
+      <c r="R34" s="162"/>
       <c r="S34" t="s">
         <v>604</v>
       </c>
@@ -18436,6 +18716,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="I31:I34"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="I27:I30"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A31:A34"/>
     <mergeCell ref="R27:R30"/>
     <mergeCell ref="R31:R34"/>
     <mergeCell ref="R2:R5"/>
@@ -18452,14 +18740,6 @@
     <mergeCell ref="I2:I5"/>
     <mergeCell ref="I6:I9"/>
     <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="I31:I34"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="I27:I30"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18467,7 +18747,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AH56"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -18492,10 +18772,10 @@
       <c r="S1" t="s">
         <v>476</v>
       </c>
-      <c r="W1" s="247" t="s">
+      <c r="W1" s="164" t="s">
         <v>376</v>
       </c>
-      <c r="X1" s="249" t="s">
+      <c r="X1" s="166" t="s">
         <v>203</v>
       </c>
       <c r="Y1" t="s">
@@ -18518,11 +18798,11 @@
       <c r="E2" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="251" t="s">
+      <c r="F2" s="168" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252"/>
+      <c r="G2" s="168"/>
+      <c r="H2" s="169"/>
       <c r="I2" s="45"/>
       <c r="N2" t="s">
         <v>471</v>
@@ -18533,14 +18813,14 @@
       <c r="S2" t="s">
         <v>520</v>
       </c>
-      <c r="W2" s="247"/>
-      <c r="X2" s="249"/>
+      <c r="W2" s="164"/>
+      <c r="X2" s="166"/>
       <c r="Y2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B3" s="253" t="s">
+      <c r="B3" s="170" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -18552,11 +18832,11 @@
       <c r="E3" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="161" t="s">
+      <c r="F3" s="162" t="s">
         <v>82</v>
       </c>
-      <c r="G3" s="161"/>
-      <c r="H3" s="176"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="173"/>
       <c r="I3" s="90" t="s">
         <v>147</v>
       </c>
@@ -18568,15 +18848,15 @@
       <c r="R3" t="s">
         <v>230</v>
       </c>
-      <c r="W3" s="248"/>
-      <c r="X3" s="250"/>
+      <c r="W3" s="165"/>
+      <c r="X3" s="167"/>
       <c r="Y3" s="8" t="s">
         <v>29</v>
       </c>
       <c r="AE3" s="129"/>
     </row>
     <row r="4" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B4" s="254"/>
+      <c r="B4" s="171"/>
       <c r="C4" s="1" t="s">
         <v>28</v>
       </c>
@@ -18586,11 +18866,11 @@
       <c r="E4" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="161" t="s">
+      <c r="F4" s="162" t="s">
         <v>81</v>
       </c>
-      <c r="G4" s="161"/>
-      <c r="H4" s="176"/>
+      <c r="G4" s="162"/>
+      <c r="H4" s="173"/>
       <c r="I4" s="45" t="s">
         <v>480</v>
       </c>
@@ -18600,31 +18880,31 @@
       <c r="S4" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="W4" s="256" t="s">
+      <c r="W4" s="174" t="s">
         <v>205</v>
       </c>
-      <c r="X4" s="231" t="s">
+      <c r="X4" s="175" t="s">
         <v>184</v>
       </c>
-      <c r="Y4" s="236" t="s">
+      <c r="Y4" s="178" t="s">
         <v>41</v>
       </c>
-      <c r="Z4" s="237"/>
-      <c r="AA4" s="238" t="s">
+      <c r="Z4" s="179"/>
+      <c r="AA4" s="180" t="s">
         <v>39</v>
       </c>
-      <c r="AB4" s="239"/>
-      <c r="AC4" s="240" t="s">
+      <c r="AB4" s="181"/>
+      <c r="AC4" s="182" t="s">
         <v>40</v>
       </c>
-      <c r="AD4" s="241"/>
-      <c r="AE4" s="242" t="s">
+      <c r="AD4" s="183"/>
+      <c r="AE4" s="184" t="s">
         <v>239</v>
       </c>
-      <c r="AF4" s="243"/>
+      <c r="AF4" s="185"/>
     </row>
     <row r="5" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B5" s="254"/>
+      <c r="B5" s="171"/>
       <c r="C5" s="1" t="s">
         <v>68</v>
       </c>
@@ -18634,11 +18914,11 @@
       <c r="E5" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="161" t="s">
+      <c r="F5" s="162" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="161"/>
-      <c r="H5" s="176"/>
+      <c r="G5" s="162"/>
+      <c r="H5" s="173"/>
       <c r="I5" s="45" t="s">
         <v>197</v>
       </c>
@@ -18648,27 +18928,27 @@
       <c r="S5" t="s">
         <v>208</v>
       </c>
-      <c r="W5" s="162"/>
-      <c r="X5" s="161"/>
-      <c r="Y5" s="244" t="s">
+      <c r="W5" s="163"/>
+      <c r="X5" s="162"/>
+      <c r="Y5" s="186" t="s">
         <v>140</v>
       </c>
-      <c r="Z5" s="234"/>
-      <c r="AA5" s="244" t="s">
+      <c r="Z5" s="177"/>
+      <c r="AA5" s="186" t="s">
         <v>351</v>
       </c>
-      <c r="AB5" s="234"/>
-      <c r="AC5" s="244" t="s">
+      <c r="AB5" s="177"/>
+      <c r="AC5" s="186" t="s">
         <v>139</v>
       </c>
-      <c r="AD5" s="234"/>
-      <c r="AE5" s="245" t="s">
+      <c r="AD5" s="177"/>
+      <c r="AE5" s="187" t="s">
         <v>419</v>
       </c>
-      <c r="AF5" s="246"/>
+      <c r="AF5" s="188"/>
     </row>
     <row r="6" spans="2:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="255"/>
+      <c r="B6" s="172"/>
       <c r="C6" s="1" t="s">
         <v>69</v>
       </c>
@@ -18678,11 +18958,11 @@
       <c r="E6" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="161" t="s">
+      <c r="F6" s="162" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="161"/>
-      <c r="H6" s="176"/>
+      <c r="G6" s="162"/>
+      <c r="H6" s="173"/>
       <c r="I6" s="91" t="s">
         <v>522</v>
       </c>
@@ -18697,10 +18977,10 @@
       <c r="U6" s="129" t="s">
         <v>473</v>
       </c>
-      <c r="W6" s="161" t="s">
+      <c r="W6" s="162" t="s">
         <v>148</v>
       </c>
-      <c r="X6" s="161" t="s">
+      <c r="X6" s="162" t="s">
         <v>185</v>
       </c>
       <c r="Y6" s="30" t="s">
@@ -18723,19 +19003,19 @@
       <c r="E7" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="233" t="s">
+      <c r="F7" s="176" t="s">
         <v>73</v>
       </c>
-      <c r="G7" s="233"/>
-      <c r="H7" s="234"/>
+      <c r="G7" s="176"/>
+      <c r="H7" s="177"/>
       <c r="P7" t="s">
         <v>207</v>
       </c>
       <c r="T7" t="s">
         <v>234</v>
       </c>
-      <c r="W7" s="161"/>
-      <c r="X7" s="161"/>
+      <c r="W7" s="162"/>
+      <c r="X7" s="162"/>
       <c r="Y7" s="30" t="s">
         <v>39</v>
       </c>
@@ -18744,21 +19024,21 @@
       </c>
     </row>
     <row r="8" spans="2:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="225" t="s">
+      <c r="B8" s="200" t="s">
         <v>98</v>
       </c>
       <c r="C8" s="99" t="s">
         <v>209</v>
       </c>
-      <c r="D8" s="223" t="s">
+      <c r="D8" s="189" t="s">
         <v>210</v>
       </c>
-      <c r="E8" s="175"/>
-      <c r="F8" s="176" t="s">
+      <c r="E8" s="190"/>
+      <c r="F8" s="173" t="s">
         <v>215</v>
       </c>
-      <c r="G8" s="223"/>
-      <c r="H8" s="223"/>
+      <c r="G8" s="189"/>
+      <c r="H8" s="189"/>
       <c r="I8" s="90" t="s">
         <v>214</v>
       </c>
@@ -18788,10 +19068,10 @@
       <c r="V8" s="41" t="s">
         <v>233</v>
       </c>
-      <c r="W8" s="161" t="s">
+      <c r="W8" s="162" t="s">
         <v>188</v>
       </c>
-      <c r="X8" s="161" t="s">
+      <c r="X8" s="162" t="s">
         <v>204</v>
       </c>
       <c r="Y8" s="30" t="s">
@@ -18802,19 +19082,19 @@
       </c>
     </row>
     <row r="9" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B9" s="226"/>
+      <c r="B9" s="201"/>
       <c r="C9" s="117" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="223" t="s">
+      <c r="D9" s="189" t="s">
         <v>80</v>
       </c>
-      <c r="E9" s="175"/>
-      <c r="F9" s="176" t="s">
+      <c r="E9" s="190"/>
+      <c r="F9" s="173" t="s">
         <v>96</v>
       </c>
-      <c r="G9" s="223"/>
-      <c r="H9" s="223"/>
+      <c r="G9" s="189"/>
+      <c r="H9" s="189"/>
       <c r="I9" s="45"/>
       <c r="N9" t="s">
         <v>425</v>
@@ -18840,8 +19120,8 @@
       <c r="V9" t="s">
         <v>235</v>
       </c>
-      <c r="W9" s="161"/>
-      <c r="X9" s="161"/>
+      <c r="W9" s="162"/>
+      <c r="X9" s="162"/>
       <c r="Y9" s="30" t="s">
         <v>239</v>
       </c>
@@ -18850,37 +19130,37 @@
       </c>
     </row>
     <row r="10" spans="2:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="226"/>
+      <c r="B10" s="201"/>
       <c r="C10" s="115" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="175" t="s">
+      <c r="D10" s="190" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="161"/>
-      <c r="F10" s="176" t="s">
+      <c r="E10" s="162"/>
+      <c r="F10" s="173" t="s">
         <v>146</v>
       </c>
-      <c r="G10" s="223"/>
-      <c r="H10" s="223"/>
+      <c r="G10" s="189"/>
+      <c r="H10" s="189"/>
       <c r="I10" s="45" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="11" spans="2:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="226"/>
+      <c r="B11" s="201"/>
       <c r="C11" s="100" t="s">
         <v>144</v>
       </c>
-      <c r="D11" s="223" t="s">
+      <c r="D11" s="189" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="175"/>
-      <c r="F11" s="176" t="s">
+      <c r="E11" s="190"/>
+      <c r="F11" s="173" t="s">
         <v>93</v>
       </c>
-      <c r="G11" s="223"/>
-      <c r="H11" s="223"/>
+      <c r="G11" s="189"/>
+      <c r="H11" s="189"/>
       <c r="I11" s="91"/>
       <c r="J11" s="26"/>
       <c r="K11" s="26"/>
@@ -18895,7 +19175,7 @@
       </c>
     </row>
     <row r="12" spans="2:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="226"/>
+      <c r="B12" s="201"/>
       <c r="C12" s="115" t="s">
         <v>275</v>
       </c>
@@ -18905,11 +19185,11 @@
       <c r="E12" s="73" t="s">
         <v>282</v>
       </c>
-      <c r="F12" s="187" t="s">
+      <c r="F12" s="191" t="s">
         <v>278</v>
       </c>
-      <c r="G12" s="235"/>
-      <c r="H12" s="235"/>
+      <c r="G12" s="192"/>
+      <c r="H12" s="192"/>
       <c r="I12" t="s">
         <v>277</v>
       </c>
@@ -18926,15 +19206,15 @@
       <c r="AB12" s="142"/>
       <c r="AC12" s="142"/>
       <c r="AD12" s="142"/>
-      <c r="AE12" s="169" t="s">
+      <c r="AE12" s="248" t="s">
         <v>452</v>
       </c>
-      <c r="AF12" s="170"/>
-      <c r="AG12" s="170"/>
-      <c r="AH12" s="171"/>
+      <c r="AF12" s="249"/>
+      <c r="AG12" s="249"/>
+      <c r="AH12" s="250"/>
     </row>
     <row r="13" spans="2:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="226"/>
+      <c r="B13" s="201"/>
       <c r="C13" s="99" t="s">
         <v>409</v>
       </c>
@@ -18944,11 +19224,11 @@
       <c r="E13" s="110" t="s">
         <v>410</v>
       </c>
-      <c r="F13" s="176" t="s">
+      <c r="F13" s="173" t="s">
         <v>412</v>
       </c>
-      <c r="G13" s="223"/>
-      <c r="H13" s="223"/>
+      <c r="G13" s="189"/>
+      <c r="H13" s="189"/>
       <c r="I13" t="s">
         <v>417</v>
       </c>
@@ -18976,7 +19256,7 @@
       </c>
     </row>
     <row r="14" spans="2:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="226"/>
+      <c r="B14" s="201"/>
       <c r="C14" s="117" t="s">
         <v>321</v>
       </c>
@@ -18986,11 +19266,11 @@
       <c r="E14" s="110" t="s">
         <v>323</v>
       </c>
-      <c r="F14" s="176" t="s">
+      <c r="F14" s="173" t="s">
         <v>344</v>
       </c>
-      <c r="G14" s="223"/>
-      <c r="H14" s="223"/>
+      <c r="G14" s="189"/>
+      <c r="H14" s="189"/>
       <c r="I14" t="s">
         <v>335</v>
       </c>
@@ -19020,7 +19300,7 @@
       </c>
     </row>
     <row r="15" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="B15" s="226"/>
+      <c r="B15" s="201"/>
       <c r="C15" s="101" t="s">
         <v>276</v>
       </c>
@@ -19030,11 +19310,11 @@
       <c r="E15" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="F15" s="183" t="s">
+      <c r="F15" s="196" t="s">
         <v>413</v>
       </c>
-      <c r="G15" s="224"/>
-      <c r="H15" s="224"/>
+      <c r="G15" s="197"/>
+      <c r="H15" s="197"/>
       <c r="I15" t="s">
         <v>467</v>
       </c>
@@ -19063,19 +19343,19 @@
       </c>
     </row>
     <row r="16" spans="2:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="226"/>
+      <c r="B16" s="201"/>
       <c r="C16" s="31" t="s">
         <v>284</v>
       </c>
-      <c r="D16" s="175" t="s">
+      <c r="D16" s="190" t="s">
         <v>283</v>
       </c>
-      <c r="E16" s="161"/>
-      <c r="F16" s="161" t="s">
+      <c r="E16" s="162"/>
+      <c r="F16" s="162" t="s">
         <v>519</v>
       </c>
-      <c r="G16" s="161"/>
-      <c r="H16" s="176"/>
+      <c r="G16" s="162"/>
+      <c r="H16" s="173"/>
       <c r="I16" s="90" t="s">
         <v>466</v>
       </c>
@@ -19122,19 +19402,19 @@
       </c>
     </row>
     <row r="17" spans="1:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="227"/>
+      <c r="B17" s="202"/>
       <c r="C17" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D17" s="182" t="s">
+      <c r="D17" s="198" t="s">
         <v>288</v>
       </c>
-      <c r="E17" s="194"/>
-      <c r="F17" s="194" t="s">
+      <c r="E17" s="199"/>
+      <c r="F17" s="199" t="s">
         <v>289</v>
       </c>
-      <c r="G17" s="194"/>
-      <c r="H17" s="183"/>
+      <c r="G17" s="199"/>
+      <c r="H17" s="196"/>
       <c r="I17" s="91" t="s">
         <v>465</v>
       </c>
@@ -19180,15 +19460,15 @@
       <c r="AB17" s="143"/>
       <c r="AC17" s="143"/>
       <c r="AD17" s="143"/>
-      <c r="AE17" s="166" t="s">
+      <c r="AE17" s="245" t="s">
         <v>451</v>
       </c>
-      <c r="AF17" s="167"/>
-      <c r="AG17" s="167"/>
-      <c r="AH17" s="168"/>
+      <c r="AF17" s="246"/>
+      <c r="AG17" s="246"/>
+      <c r="AH17" s="247"/>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="B18" s="228" t="s">
+      <c r="B18" s="203" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="31" t="s">
@@ -19200,12 +19480,12 @@
       <c r="E18" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="F18" s="231" t="s">
+      <c r="F18" s="175" t="s">
         <v>60</v>
       </c>
-      <c r="G18" s="231"/>
-      <c r="H18" s="187"/>
-      <c r="I18" s="232" t="s">
+      <c r="G18" s="175"/>
+      <c r="H18" s="191"/>
+      <c r="I18" s="206" t="s">
         <v>370</v>
       </c>
       <c r="J18" t="s">
@@ -19261,7 +19541,7 @@
       </c>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="B19" s="229"/>
+      <c r="B19" s="204"/>
       <c r="C19" s="1" t="s">
         <v>45</v>
       </c>
@@ -19271,12 +19551,12 @@
       <c r="E19" s="110" t="s">
         <v>44</v>
       </c>
-      <c r="F19" s="161" t="s">
+      <c r="F19" s="162" t="s">
         <v>50</v>
       </c>
-      <c r="G19" s="161"/>
-      <c r="H19" s="176"/>
-      <c r="I19" s="175"/>
+      <c r="G19" s="162"/>
+      <c r="H19" s="173"/>
+      <c r="I19" s="190"/>
       <c r="J19" t="s">
         <v>138</v>
       </c>
@@ -19305,7 +19585,7 @@
       </c>
     </row>
     <row r="20" spans="1:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="229"/>
+      <c r="B20" s="204"/>
       <c r="C20" s="1" t="s">
         <v>52</v>
       </c>
@@ -19315,12 +19595,12 @@
       <c r="E20" s="110" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="161" t="s">
+      <c r="F20" s="162" t="s">
         <v>74</v>
       </c>
-      <c r="G20" s="161"/>
-      <c r="H20" s="176"/>
-      <c r="I20" s="175"/>
+      <c r="G20" s="162"/>
+      <c r="H20" s="173"/>
+      <c r="I20" s="190"/>
       <c r="J20" t="s">
         <v>464</v>
       </c>
@@ -19364,7 +19644,7 @@
       </c>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="B21" s="229"/>
+      <c r="B21" s="204"/>
       <c r="C21" s="32" t="s">
         <v>51</v>
       </c>
@@ -19374,12 +19654,12 @@
       <c r="E21" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="F21" s="194" t="s">
+      <c r="F21" s="199" t="s">
         <v>10</v>
       </c>
-      <c r="G21" s="194"/>
-      <c r="H21" s="183"/>
-      <c r="I21" s="175"/>
+      <c r="G21" s="199"/>
+      <c r="H21" s="196"/>
+      <c r="I21" s="190"/>
       <c r="J21" t="s">
         <v>512</v>
       </c>
@@ -19416,7 +19696,7 @@
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="B22" s="229"/>
+      <c r="B22" s="204"/>
       <c r="C22" s="6" t="s">
         <v>1</v>
       </c>
@@ -19426,11 +19706,11 @@
       <c r="E22" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="161" t="s">
+      <c r="F22" s="162" t="s">
         <v>18</v>
       </c>
-      <c r="G22" s="161"/>
-      <c r="H22" s="176"/>
+      <c r="G22" s="162"/>
+      <c r="H22" s="173"/>
       <c r="I22" s="90"/>
       <c r="J22" s="24"/>
       <c r="K22" s="24"/>
@@ -19457,15 +19737,15 @@
       <c r="AB22" s="145"/>
       <c r="AC22" s="145"/>
       <c r="AD22" s="145"/>
-      <c r="AE22" s="163" t="s">
+      <c r="AE22" s="242" t="s">
         <v>450</v>
       </c>
-      <c r="AF22" s="164"/>
-      <c r="AG22" s="164"/>
-      <c r="AH22" s="165"/>
+      <c r="AF22" s="243"/>
+      <c r="AG22" s="243"/>
+      <c r="AH22" s="244"/>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="B23" s="229"/>
+      <c r="B23" s="204"/>
       <c r="C23" s="6" t="s">
         <v>43</v>
       </c>
@@ -19475,11 +19755,11 @@
       <c r="E23" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="F23" s="161" t="s">
+      <c r="F23" s="162" t="s">
         <v>54</v>
       </c>
-      <c r="G23" s="161"/>
-      <c r="H23" s="176"/>
+      <c r="G23" s="162"/>
+      <c r="H23" s="173"/>
       <c r="I23" s="45"/>
       <c r="N23" s="17" t="s">
         <v>265</v>
@@ -19519,7 +19799,7 @@
       </c>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="B24" s="229"/>
+      <c r="B24" s="204"/>
       <c r="C24" s="6" t="s">
         <v>55</v>
       </c>
@@ -19529,11 +19809,11 @@
       <c r="E24" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="161" t="s">
+      <c r="F24" s="162" t="s">
         <v>57</v>
       </c>
-      <c r="G24" s="161"/>
-      <c r="H24" s="176"/>
+      <c r="G24" s="162"/>
+      <c r="H24" s="173"/>
       <c r="I24" s="45"/>
       <c r="Y24" s="11"/>
       <c r="Z24" s="69" t="s">
@@ -19557,7 +19837,7 @@
       </c>
     </row>
     <row r="25" spans="1:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="230"/>
+      <c r="B25" s="205"/>
       <c r="C25" s="6" t="s">
         <v>0</v>
       </c>
@@ -19567,11 +19847,11 @@
       <c r="E25" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="F25" s="161" t="s">
+      <c r="F25" s="162" t="s">
         <v>17</v>
       </c>
-      <c r="G25" s="161"/>
-      <c r="H25" s="176"/>
+      <c r="G25" s="162"/>
+      <c r="H25" s="173"/>
       <c r="I25" s="91"/>
       <c r="J25" s="26"/>
       <c r="K25" s="26"/>
@@ -19616,11 +19896,11 @@
       <c r="E26" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F26" s="233" t="s">
+      <c r="F26" s="176" t="s">
         <v>48</v>
       </c>
-      <c r="G26" s="233"/>
-      <c r="H26" s="234"/>
+      <c r="G26" s="176"/>
+      <c r="H26" s="177"/>
       <c r="I26" t="s">
         <v>192</v>
       </c>
@@ -19629,12 +19909,12 @@
       <c r="N26" s="113" t="s">
         <v>250</v>
       </c>
-      <c r="O26" s="220" t="s">
+      <c r="O26" s="193" t="s">
         <v>9</v>
       </c>
-      <c r="P26" s="221"/>
-      <c r="Q26" s="221"/>
-      <c r="R26" s="222"/>
+      <c r="P26" s="194"/>
+      <c r="Q26" s="194"/>
+      <c r="R26" s="195"/>
       <c r="S26" s="114" t="s">
         <v>246</v>
       </c>
@@ -19716,12 +19996,12 @@
       <c r="AB27" s="144"/>
       <c r="AC27" s="144"/>
       <c r="AD27" s="144"/>
-      <c r="AE27" s="198" t="s">
+      <c r="AE27" s="222" t="s">
         <v>449</v>
       </c>
-      <c r="AF27" s="199"/>
-      <c r="AG27" s="199"/>
-      <c r="AH27" s="200"/>
+      <c r="AF27" s="223"/>
+      <c r="AG27" s="223"/>
+      <c r="AH27" s="224"/>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.3">
       <c r="N28" s="108" t="s">
@@ -19844,19 +20124,19 @@
       <c r="B30" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C30" s="214" t="s">
+      <c r="C30" s="207" t="s">
         <v>99</v>
       </c>
-      <c r="D30" s="214"/>
-      <c r="E30" s="214"/>
-      <c r="F30" s="214"/>
+      <c r="D30" s="207"/>
+      <c r="E30" s="207"/>
+      <c r="F30" s="207"/>
       <c r="G30" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="H30" s="215" t="s">
+      <c r="H30" s="208" t="s">
         <v>525</v>
       </c>
-      <c r="I30" s="216"/>
+      <c r="I30" s="209"/>
       <c r="N30" s="94" t="s">
         <v>373</v>
       </c>
@@ -19943,24 +20223,24 @@
       <c r="B33" s="14" t="s">
         <v>549</v>
       </c>
-      <c r="N33" s="195" t="s">
+      <c r="N33" s="210" t="s">
         <v>86</v>
       </c>
-      <c r="O33" s="196"/>
-      <c r="P33" s="195" t="s">
+      <c r="O33" s="211"/>
+      <c r="P33" s="210" t="s">
         <v>46</v>
       </c>
-      <c r="Q33" s="196"/>
-      <c r="R33" s="195" t="s">
+      <c r="Q33" s="211"/>
+      <c r="R33" s="210" t="s">
         <v>179</v>
       </c>
-      <c r="S33" s="196"/>
-      <c r="T33" s="197"/>
-      <c r="U33" s="195" t="s">
+      <c r="S33" s="211"/>
+      <c r="T33" s="212"/>
+      <c r="U33" s="210" t="s">
         <v>180</v>
       </c>
-      <c r="V33" s="196"/>
-      <c r="W33" s="197"/>
+      <c r="V33" s="211"/>
+      <c r="W33" s="212"/>
       <c r="Y33" s="8" t="s">
         <v>189</v>
       </c>
@@ -20000,21 +20280,21 @@
       <c r="W34" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="Z34" s="217" t="s">
+      <c r="Z34" s="219" t="s">
         <v>558</v>
       </c>
-      <c r="AA34" s="218"/>
-      <c r="AB34" s="219"/>
-      <c r="AC34" s="217" t="s">
+      <c r="AA34" s="220"/>
+      <c r="AB34" s="221"/>
+      <c r="AC34" s="219" t="s">
         <v>569</v>
       </c>
-      <c r="AD34" s="219"/>
-      <c r="AE34" s="218" t="s">
+      <c r="AD34" s="221"/>
+      <c r="AE34" s="220" t="s">
         <v>564</v>
       </c>
-      <c r="AF34" s="218"/>
-      <c r="AG34" s="218"/>
-      <c r="AH34" s="219"/>
+      <c r="AF34" s="220"/>
+      <c r="AG34" s="220"/>
+      <c r="AH34" s="221"/>
     </row>
     <row r="35" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B35" s="14" t="s">
@@ -20046,27 +20326,27 @@
       <c r="W35" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="X35" s="201" t="s">
+      <c r="X35" s="225" t="s">
         <v>75</v>
       </c>
       <c r="Y35" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="Z35" s="211" t="s">
+      <c r="Z35" s="232" t="s">
         <v>4</v>
       </c>
-      <c r="AA35" s="212"/>
-      <c r="AB35" s="213"/>
-      <c r="AC35" s="186" t="s">
+      <c r="AA35" s="233"/>
+      <c r="AB35" s="234"/>
+      <c r="AC35" s="235" t="s">
         <v>559</v>
       </c>
-      <c r="AD35" s="187"/>
-      <c r="AE35" s="205" t="s">
+      <c r="AD35" s="191"/>
+      <c r="AE35" s="229" t="s">
         <v>560</v>
       </c>
-      <c r="AF35" s="206"/>
-      <c r="AG35" s="206"/>
-      <c r="AH35" s="207"/>
+      <c r="AF35" s="230"/>
+      <c r="AG35" s="230"/>
+      <c r="AH35" s="231"/>
     </row>
     <row r="36" spans="2:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="14" t="s">
@@ -20097,25 +20377,25 @@
       <c r="W36" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="X36" s="201"/>
+      <c r="X36" s="225"/>
       <c r="Y36" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="Z36" s="208" t="s">
+      <c r="Z36" s="213" t="s">
         <v>563</v>
       </c>
-      <c r="AA36" s="209"/>
-      <c r="AB36" s="210"/>
-      <c r="AC36" s="175" t="s">
+      <c r="AA36" s="214"/>
+      <c r="AB36" s="215"/>
+      <c r="AC36" s="190" t="s">
         <v>164</v>
       </c>
-      <c r="AD36" s="176"/>
-      <c r="AE36" s="172" t="s">
+      <c r="AD36" s="173"/>
+      <c r="AE36" s="216" t="s">
         <v>572</v>
       </c>
-      <c r="AF36" s="173"/>
-      <c r="AG36" s="173"/>
-      <c r="AH36" s="174"/>
+      <c r="AF36" s="217"/>
+      <c r="AG36" s="217"/>
+      <c r="AH36" s="218"/>
     </row>
     <row r="37" spans="2:34" x14ac:dyDescent="0.3">
       <c r="N37" s="94" t="s">
@@ -20144,25 +20424,25 @@
       <c r="W37" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="X37" s="201"/>
+      <c r="X37" s="225"/>
       <c r="Y37" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="Z37" s="208" t="s">
+      <c r="Z37" s="213" t="s">
         <v>565</v>
       </c>
-      <c r="AA37" s="209"/>
-      <c r="AB37" s="210"/>
-      <c r="AC37" s="175" t="s">
+      <c r="AA37" s="214"/>
+      <c r="AB37" s="215"/>
+      <c r="AC37" s="190" t="s">
         <v>191</v>
       </c>
-      <c r="AD37" s="176"/>
-      <c r="AE37" s="172" t="s">
+      <c r="AD37" s="173"/>
+      <c r="AE37" s="216" t="s">
         <v>571</v>
       </c>
-      <c r="AF37" s="173"/>
-      <c r="AG37" s="173"/>
-      <c r="AH37" s="174"/>
+      <c r="AF37" s="217"/>
+      <c r="AG37" s="217"/>
+      <c r="AH37" s="218"/>
     </row>
     <row r="38" spans="2:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="8" t="s">
@@ -20189,25 +20469,25 @@
       <c r="K38" s="123" t="s">
         <v>340</v>
       </c>
-      <c r="X38" s="201"/>
+      <c r="X38" s="225"/>
       <c r="Y38" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="Z38" s="191" t="s">
+      <c r="Z38" s="236" t="s">
         <v>562</v>
       </c>
-      <c r="AA38" s="192"/>
-      <c r="AB38" s="193"/>
-      <c r="AC38" s="182" t="s">
+      <c r="AA38" s="237"/>
+      <c r="AB38" s="238"/>
+      <c r="AC38" s="198" t="s">
         <v>163</v>
       </c>
-      <c r="AD38" s="183"/>
-      <c r="AE38" s="179" t="s">
+      <c r="AD38" s="196"/>
+      <c r="AE38" s="239" t="s">
         <v>584</v>
       </c>
-      <c r="AF38" s="180"/>
-      <c r="AG38" s="180"/>
-      <c r="AH38" s="181"/>
+      <c r="AF38" s="240"/>
+      <c r="AG38" s="240"/>
+      <c r="AH38" s="241"/>
     </row>
     <row r="39" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B39" s="77" t="s">
@@ -20232,27 +20512,27 @@
       <c r="O39" t="s">
         <v>424</v>
       </c>
-      <c r="X39" s="201" t="s">
+      <c r="X39" s="225" t="s">
         <v>552</v>
       </c>
       <c r="Y39" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="Z39" s="202" t="s">
+      <c r="Z39" s="226" t="s">
         <v>574</v>
       </c>
-      <c r="AA39" s="203"/>
-      <c r="AB39" s="204"/>
-      <c r="AC39" s="175" t="s">
+      <c r="AA39" s="227"/>
+      <c r="AB39" s="228"/>
+      <c r="AC39" s="190" t="s">
         <v>575</v>
       </c>
-      <c r="AD39" s="161"/>
-      <c r="AE39" s="205" t="s">
+      <c r="AD39" s="162"/>
+      <c r="AE39" s="229" t="s">
         <v>573</v>
       </c>
-      <c r="AF39" s="206"/>
-      <c r="AG39" s="206"/>
-      <c r="AH39" s="207"/>
+      <c r="AF39" s="230"/>
+      <c r="AG39" s="230"/>
+      <c r="AH39" s="231"/>
     </row>
     <row r="40" spans="2:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="78" t="s">
@@ -20274,10 +20554,10 @@
       <c r="N40" s="42" t="s">
         <v>508</v>
       </c>
-      <c r="O40" s="186" t="s">
+      <c r="O40" s="235" t="s">
         <v>509</v>
       </c>
-      <c r="P40" s="187"/>
+      <c r="P40" s="191"/>
       <c r="Q40" s="42" t="s">
         <v>331</v>
       </c>
@@ -20296,25 +20576,25 @@
       <c r="V40" s="146" t="s">
         <v>420</v>
       </c>
-      <c r="X40" s="201"/>
+      <c r="X40" s="225"/>
       <c r="Y40" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="Z40" s="208" t="s">
+      <c r="Z40" s="213" t="s">
         <v>576</v>
       </c>
-      <c r="AA40" s="209"/>
-      <c r="AB40" s="210"/>
-      <c r="AC40" s="175" t="s">
+      <c r="AA40" s="214"/>
+      <c r="AB40" s="215"/>
+      <c r="AC40" s="190" t="s">
         <v>182</v>
       </c>
-      <c r="AD40" s="161"/>
-      <c r="AE40" s="172" t="s">
+      <c r="AD40" s="162"/>
+      <c r="AE40" s="216" t="s">
         <v>577</v>
       </c>
-      <c r="AF40" s="173"/>
-      <c r="AG40" s="173"/>
-      <c r="AH40" s="174"/>
+      <c r="AF40" s="217"/>
+      <c r="AG40" s="217"/>
+      <c r="AH40" s="218"/>
     </row>
     <row r="41" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B41" s="78" t="s">
@@ -20332,8 +20612,8 @@
       <c r="K41" s="82" t="s">
         <v>566</v>
       </c>
-      <c r="O41" s="182"/>
-      <c r="P41" s="183"/>
+      <c r="O41" s="198"/>
+      <c r="P41" s="196"/>
       <c r="R41" s="37" t="s">
         <v>56</v>
       </c>
@@ -20346,49 +20626,49 @@
       <c r="V41" s="146" t="s">
         <v>427</v>
       </c>
-      <c r="X41" s="201"/>
+      <c r="X41" s="225"/>
       <c r="Y41" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="Z41" s="208" t="s">
+      <c r="Z41" s="213" t="s">
         <v>581</v>
       </c>
-      <c r="AA41" s="209"/>
-      <c r="AB41" s="210"/>
-      <c r="AC41" s="175" t="s">
+      <c r="AA41" s="214"/>
+      <c r="AB41" s="215"/>
+      <c r="AC41" s="190" t="s">
         <v>165</v>
       </c>
-      <c r="AD41" s="161"/>
-      <c r="AE41" s="172" t="s">
+      <c r="AD41" s="162"/>
+      <c r="AE41" s="216" t="s">
         <v>582</v>
       </c>
-      <c r="AF41" s="173"/>
-      <c r="AG41" s="173"/>
-      <c r="AH41" s="174"/>
+      <c r="AF41" s="217"/>
+      <c r="AG41" s="217"/>
+      <c r="AH41" s="218"/>
     </row>
     <row r="42" spans="2:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="N42" s="89" t="s">
         <v>459</v>
       </c>
-      <c r="X42" s="201"/>
+      <c r="X42" s="225"/>
       <c r="Y42" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="Z42" s="191" t="s">
+      <c r="Z42" s="236" t="s">
         <v>579</v>
       </c>
-      <c r="AA42" s="192"/>
-      <c r="AB42" s="193"/>
-      <c r="AC42" s="182" t="s">
+      <c r="AA42" s="237"/>
+      <c r="AB42" s="238"/>
+      <c r="AC42" s="198" t="s">
         <v>166</v>
       </c>
-      <c r="AD42" s="194"/>
-      <c r="AE42" s="179" t="s">
+      <c r="AD42" s="199"/>
+      <c r="AE42" s="239" t="s">
         <v>580</v>
       </c>
-      <c r="AF42" s="180"/>
-      <c r="AG42" s="180"/>
-      <c r="AH42" s="181"/>
+      <c r="AF42" s="240"/>
+      <c r="AG42" s="240"/>
+      <c r="AH42" s="241"/>
     </row>
     <row r="43" spans="2:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="8" t="s">
@@ -20409,21 +20689,21 @@
     </row>
     <row r="44" spans="2:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="5"/>
-      <c r="C44" s="195" t="s">
+      <c r="C44" s="210" t="s">
         <v>220</v>
       </c>
-      <c r="D44" s="196"/>
-      <c r="E44" s="196"/>
-      <c r="F44" s="196"/>
-      <c r="G44" s="197"/>
-      <c r="H44" s="195" t="s">
+      <c r="D44" s="211"/>
+      <c r="E44" s="211"/>
+      <c r="F44" s="211"/>
+      <c r="G44" s="212"/>
+      <c r="H44" s="210" t="s">
         <v>221</v>
       </c>
-      <c r="I44" s="197"/>
-      <c r="J44" s="195" t="s">
+      <c r="I44" s="212"/>
+      <c r="J44" s="210" t="s">
         <v>223</v>
       </c>
-      <c r="K44" s="197"/>
+      <c r="K44" s="212"/>
       <c r="N44" s="5" t="s">
         <v>297</v>
       </c>
@@ -20450,21 +20730,21 @@
       <c r="B45" s="83" t="s">
         <v>172</v>
       </c>
-      <c r="C45" s="172" t="s">
+      <c r="C45" s="216" t="s">
         <v>279</v>
       </c>
-      <c r="D45" s="173"/>
-      <c r="E45" s="173"/>
-      <c r="F45" s="173"/>
-      <c r="G45" s="174"/>
-      <c r="H45" s="186" t="s">
+      <c r="D45" s="217"/>
+      <c r="E45" s="217"/>
+      <c r="F45" s="217"/>
+      <c r="G45" s="218"/>
+      <c r="H45" s="235" t="s">
         <v>217</v>
       </c>
-      <c r="I45" s="187"/>
-      <c r="J45" s="186" t="s">
+      <c r="I45" s="191"/>
+      <c r="J45" s="235" t="s">
         <v>350</v>
       </c>
-      <c r="K45" s="187"/>
+      <c r="K45" s="191"/>
       <c r="N45" s="103" t="s">
         <v>296</v>
       </c>
@@ -20477,12 +20757,12 @@
       <c r="S45" s="103" t="s">
         <v>299</v>
       </c>
-      <c r="T45" s="188" t="s">
+      <c r="T45" s="255" t="s">
         <v>302</v>
       </c>
-      <c r="U45" s="189"/>
-      <c r="V45" s="189"/>
-      <c r="W45" s="190"/>
+      <c r="U45" s="256"/>
+      <c r="V45" s="256"/>
+      <c r="W45" s="257"/>
       <c r="Y45" s="8" t="s">
         <v>66</v>
       </c>
@@ -20494,21 +20774,21 @@
       <c r="B46" s="84" t="s">
         <v>183</v>
       </c>
-      <c r="C46" s="172" t="s">
+      <c r="C46" s="216" t="s">
         <v>228</v>
       </c>
-      <c r="D46" s="173"/>
-      <c r="E46" s="173"/>
-      <c r="F46" s="173"/>
-      <c r="G46" s="174"/>
-      <c r="H46" s="175" t="s">
+      <c r="D46" s="217"/>
+      <c r="E46" s="217"/>
+      <c r="F46" s="217"/>
+      <c r="G46" s="218"/>
+      <c r="H46" s="190" t="s">
         <v>218</v>
       </c>
-      <c r="I46" s="176"/>
-      <c r="J46" s="175" t="s">
+      <c r="I46" s="173"/>
+      <c r="J46" s="190" t="s">
         <v>243</v>
       </c>
-      <c r="K46" s="176"/>
+      <c r="K46" s="173"/>
       <c r="Y46" s="8" t="s">
         <v>168</v>
       </c>
@@ -20520,21 +20800,21 @@
       <c r="B47" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C47" s="172" t="s">
+      <c r="C47" s="216" t="s">
         <v>280</v>
       </c>
-      <c r="D47" s="173"/>
-      <c r="E47" s="173"/>
-      <c r="F47" s="173"/>
-      <c r="G47" s="174"/>
-      <c r="H47" s="175" t="s">
+      <c r="D47" s="217"/>
+      <c r="E47" s="217"/>
+      <c r="F47" s="217"/>
+      <c r="G47" s="218"/>
+      <c r="H47" s="190" t="s">
         <v>225</v>
       </c>
-      <c r="I47" s="176"/>
-      <c r="J47" s="175" t="s">
+      <c r="I47" s="173"/>
+      <c r="J47" s="190" t="s">
         <v>290</v>
       </c>
-      <c r="K47" s="176"/>
+      <c r="K47" s="173"/>
       <c r="N47" s="8" t="s">
         <v>293</v>
       </c>
@@ -20544,10 +20824,10 @@
       <c r="R47" s="106" t="s">
         <v>291</v>
       </c>
-      <c r="S47" s="177" t="s">
+      <c r="S47" s="251" t="s">
         <v>295</v>
       </c>
-      <c r="T47" s="178"/>
+      <c r="T47" s="252"/>
       <c r="U47" t="s">
         <v>303</v>
       </c>
@@ -20562,31 +20842,31 @@
       <c r="B48" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="C48" s="179" t="s">
+      <c r="C48" s="239" t="s">
         <v>229</v>
       </c>
-      <c r="D48" s="180"/>
-      <c r="E48" s="180"/>
-      <c r="F48" s="180"/>
-      <c r="G48" s="181"/>
-      <c r="H48" s="182" t="s">
+      <c r="D48" s="240"/>
+      <c r="E48" s="240"/>
+      <c r="F48" s="240"/>
+      <c r="G48" s="241"/>
+      <c r="H48" s="198" t="s">
         <v>216</v>
       </c>
-      <c r="I48" s="183"/>
-      <c r="J48" s="182" t="s">
+      <c r="I48" s="196"/>
+      <c r="J48" s="198" t="s">
         <v>226</v>
       </c>
-      <c r="K48" s="183"/>
+      <c r="K48" s="196"/>
       <c r="N48" t="s">
         <v>447</v>
       </c>
       <c r="R48" s="107" t="s">
         <v>292</v>
       </c>
-      <c r="S48" s="184" t="s">
+      <c r="S48" s="253" t="s">
         <v>294</v>
       </c>
-      <c r="T48" s="185"/>
+      <c r="T48" s="254"/>
       <c r="U48" t="s">
         <v>304</v>
       </c>
@@ -20620,92 +20900,6 @@
     <row r="56" spans="14:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="110">
-    <mergeCell ref="W1:W3"/>
-    <mergeCell ref="X1:X3"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="X4:X5"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="W6:W7"/>
-    <mergeCell ref="X6:X7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AC4:AD4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="AC5:AD5"/>
-    <mergeCell ref="AE5:AF5"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="B8:B17"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="B18:B25"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:I21"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="R33:T33"/>
-    <mergeCell ref="U33:W33"/>
-    <mergeCell ref="Z37:AB37"/>
-    <mergeCell ref="AC37:AD37"/>
-    <mergeCell ref="AE37:AH37"/>
-    <mergeCell ref="Z34:AB34"/>
-    <mergeCell ref="AC34:AD34"/>
-    <mergeCell ref="AE34:AH34"/>
-    <mergeCell ref="AE27:AH27"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="X39:X42"/>
-    <mergeCell ref="Z39:AB39"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="AE39:AH39"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="AC40:AD40"/>
-    <mergeCell ref="AE40:AH40"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="AC41:AD41"/>
-    <mergeCell ref="X35:X38"/>
-    <mergeCell ref="Z35:AB35"/>
-    <mergeCell ref="AC35:AD35"/>
-    <mergeCell ref="AE35:AH35"/>
-    <mergeCell ref="Z36:AB36"/>
-    <mergeCell ref="AC36:AD36"/>
-    <mergeCell ref="AE36:AH36"/>
-    <mergeCell ref="Z38:AB38"/>
-    <mergeCell ref="AC38:AD38"/>
-    <mergeCell ref="AE38:AH38"/>
-    <mergeCell ref="O40:P41"/>
     <mergeCell ref="AE22:AH22"/>
     <mergeCell ref="AE17:AH17"/>
     <mergeCell ref="AE12:AH12"/>
@@ -20730,6 +20924,92 @@
     <mergeCell ref="AE42:AH42"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="H44:I44"/>
+    <mergeCell ref="AE27:AH27"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="X39:X42"/>
+    <mergeCell ref="Z39:AB39"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="AE39:AH39"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="AC40:AD40"/>
+    <mergeCell ref="AE40:AH40"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="AC41:AD41"/>
+    <mergeCell ref="X35:X38"/>
+    <mergeCell ref="Z35:AB35"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AE35:AH35"/>
+    <mergeCell ref="Z36:AB36"/>
+    <mergeCell ref="AC36:AD36"/>
+    <mergeCell ref="AE36:AH36"/>
+    <mergeCell ref="Z38:AB38"/>
+    <mergeCell ref="AC38:AD38"/>
+    <mergeCell ref="AE38:AH38"/>
+    <mergeCell ref="O40:P41"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="R33:T33"/>
+    <mergeCell ref="U33:W33"/>
+    <mergeCell ref="Z37:AB37"/>
+    <mergeCell ref="AC37:AD37"/>
+    <mergeCell ref="AE37:AH37"/>
+    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="AC34:AD34"/>
+    <mergeCell ref="AE34:AH34"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B8:B17"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="B18:B25"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:I21"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AC4:AD4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="AA5:AB5"/>
+    <mergeCell ref="AC5:AD5"/>
+    <mergeCell ref="AE5:AF5"/>
+    <mergeCell ref="W1:W3"/>
+    <mergeCell ref="X1:X3"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="X4:X5"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="W6:W7"/>
+    <mergeCell ref="X6:X7"/>
+    <mergeCell ref="F7:H7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20738,7 +21018,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AO48"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -20782,10 +21062,10 @@
       <c r="B3" s="34">
         <v>1</v>
       </c>
-      <c r="C3" s="257" t="s">
+      <c r="C3" s="260" t="s">
         <v>481</v>
       </c>
-      <c r="D3" s="257"/>
+      <c r="D3" s="260"/>
       <c r="E3" t="s">
         <v>133</v>
       </c>
@@ -20809,10 +21089,10 @@
       <c r="B4" s="34">
         <v>2</v>
       </c>
-      <c r="C4" s="257" t="s">
+      <c r="C4" s="260" t="s">
         <v>482</v>
       </c>
-      <c r="D4" s="257"/>
+      <c r="D4" s="260"/>
       <c r="E4" t="s">
         <v>404</v>
       </c>
@@ -20825,10 +21105,10 @@
       <c r="B5" s="34">
         <v>3</v>
       </c>
-      <c r="C5" s="257" t="s">
+      <c r="C5" s="260" t="s">
         <v>483</v>
       </c>
-      <c r="D5" s="257"/>
+      <c r="D5" s="260"/>
       <c r="E5" t="s">
         <v>405</v>
       </c>
@@ -20840,10 +21120,10 @@
       <c r="B6" s="34">
         <v>4</v>
       </c>
-      <c r="C6" s="257" t="s">
+      <c r="C6" s="260" t="s">
         <v>484</v>
       </c>
-      <c r="D6" s="257"/>
+      <c r="D6" s="260"/>
       <c r="E6" t="s">
         <v>486</v>
       </c>
@@ -20855,10 +21135,10 @@
       <c r="B7" s="34">
         <v>5</v>
       </c>
-      <c r="C7" s="257" t="s">
+      <c r="C7" s="260" t="s">
         <v>130</v>
       </c>
-      <c r="D7" s="257"/>
+      <c r="D7" s="260"/>
       <c r="E7" t="s">
         <v>497</v>
       </c>
@@ -20867,10 +21147,10 @@
       <c r="B8" s="34">
         <v>6</v>
       </c>
-      <c r="C8" s="257" t="s">
+      <c r="C8" s="260" t="s">
         <v>131</v>
       </c>
-      <c r="D8" s="257"/>
+      <c r="D8" s="260"/>
       <c r="E8" t="s">
         <v>487</v>
       </c>
@@ -20882,10 +21162,10 @@
       <c r="B9" s="34">
         <v>7</v>
       </c>
-      <c r="C9" s="257" t="s">
+      <c r="C9" s="260" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="257"/>
+      <c r="D9" s="260"/>
       <c r="E9" t="s">
         <v>485</v>
       </c>
@@ -20897,10 +21177,10 @@
       <c r="B10" s="34">
         <v>8</v>
       </c>
-      <c r="C10" s="257" t="s">
+      <c r="C10" s="260" t="s">
         <v>183</v>
       </c>
-      <c r="D10" s="257"/>
+      <c r="D10" s="260"/>
       <c r="E10" t="s">
         <v>305</v>
       </c>
@@ -20919,10 +21199,10 @@
       <c r="B12" s="33">
         <v>1</v>
       </c>
-      <c r="C12" s="259" t="s">
+      <c r="C12" s="261" t="s">
         <v>116</v>
       </c>
-      <c r="D12" s="259"/>
+      <c r="D12" s="261"/>
       <c r="E12" t="s">
         <v>136</v>
       </c>
@@ -20931,10 +21211,10 @@
       <c r="B13" s="33">
         <v>2</v>
       </c>
-      <c r="C13" s="259" t="s">
+      <c r="C13" s="261" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="259"/>
+      <c r="D13" s="261"/>
       <c r="E13" t="s">
         <v>491</v>
       </c>
@@ -20946,10 +21226,10 @@
       <c r="B14" s="33">
         <v>3</v>
       </c>
-      <c r="C14" s="259" t="s">
+      <c r="C14" s="261" t="s">
         <v>118</v>
       </c>
-      <c r="D14" s="259"/>
+      <c r="D14" s="261"/>
       <c r="E14" t="s">
         <v>489</v>
       </c>
@@ -20961,10 +21241,10 @@
       <c r="B15" s="33">
         <v>4</v>
       </c>
-      <c r="C15" s="259" t="s">
+      <c r="C15" s="261" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="259"/>
+      <c r="D15" s="261"/>
       <c r="E15" t="s">
         <v>365</v>
       </c>
@@ -20973,10 +21253,10 @@
       <c r="B16" s="33">
         <v>5</v>
       </c>
-      <c r="C16" s="259" t="s">
+      <c r="C16" s="261" t="s">
         <v>308</v>
       </c>
-      <c r="D16" s="259"/>
+      <c r="D16" s="261"/>
       <c r="E16" t="s">
         <v>399</v>
       </c>
@@ -21001,10 +21281,10 @@
       <c r="B17" s="33">
         <v>6</v>
       </c>
-      <c r="C17" s="259" t="s">
+      <c r="C17" s="261" t="s">
         <v>309</v>
       </c>
-      <c r="D17" s="259"/>
+      <c r="D17" s="261"/>
       <c r="E17" t="s">
         <v>379</v>
       </c>
@@ -21013,10 +21293,10 @@
       <c r="B18" s="33">
         <v>7</v>
       </c>
-      <c r="C18" s="259" t="s">
+      <c r="C18" s="261" t="s">
         <v>134</v>
       </c>
-      <c r="D18" s="259"/>
+      <c r="D18" s="261"/>
       <c r="E18" t="s">
         <v>135</v>
       </c>
@@ -21025,10 +21305,10 @@
       <c r="B19" s="33">
         <v>8</v>
       </c>
-      <c r="C19" s="259" t="s">
+      <c r="C19" s="261" t="s">
         <v>132</v>
       </c>
-      <c r="D19" s="259"/>
+      <c r="D19" s="261"/>
       <c r="E19" t="s">
         <v>492</v>
       </c>
@@ -21043,10 +21323,10 @@
       <c r="B21" s="35">
         <v>1</v>
       </c>
-      <c r="C21" s="258" t="s">
+      <c r="C21" s="259" t="s">
         <v>103</v>
       </c>
-      <c r="D21" s="258"/>
+      <c r="D21" s="259"/>
       <c r="E21" t="s">
         <v>493</v>
       </c>
@@ -21055,10 +21335,10 @@
       <c r="B22" s="35">
         <v>2</v>
       </c>
-      <c r="C22" s="258" t="s">
+      <c r="C22" s="259" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="258"/>
+      <c r="D22" s="259"/>
       <c r="E22" t="s">
         <v>494</v>
       </c>
@@ -21067,10 +21347,10 @@
       <c r="B23" s="35">
         <v>3</v>
       </c>
-      <c r="C23" s="258" t="s">
+      <c r="C23" s="259" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="258"/>
+      <c r="D23" s="259"/>
       <c r="E23" t="s">
         <v>495</v>
       </c>
@@ -21079,10 +21359,10 @@
       <c r="B24" s="35">
         <v>4</v>
       </c>
-      <c r="C24" s="258" t="s">
+      <c r="C24" s="259" t="s">
         <v>106</v>
       </c>
-      <c r="D24" s="258"/>
+      <c r="D24" s="259"/>
       <c r="E24" t="s">
         <v>500</v>
       </c>
@@ -21091,10 +21371,10 @@
       <c r="B25" s="35">
         <v>5</v>
       </c>
-      <c r="C25" s="258" t="s">
+      <c r="C25" s="259" t="s">
         <v>108</v>
       </c>
-      <c r="D25" s="258"/>
+      <c r="D25" s="259"/>
       <c r="E25" t="s">
         <v>496</v>
       </c>
@@ -21103,10 +21383,10 @@
       <c r="B26" s="35">
         <v>6</v>
       </c>
-      <c r="C26" s="258" t="s">
+      <c r="C26" s="259" t="s">
         <v>109</v>
       </c>
-      <c r="D26" s="258"/>
+      <c r="D26" s="259"/>
       <c r="E26" t="s">
         <v>498</v>
       </c>
@@ -21115,10 +21395,10 @@
       <c r="B27" s="35">
         <v>7</v>
       </c>
-      <c r="C27" s="258" t="s">
+      <c r="C27" s="259" t="s">
         <v>110</v>
       </c>
-      <c r="D27" s="258"/>
+      <c r="D27" s="259"/>
       <c r="E27" t="s">
         <v>499</v>
       </c>
@@ -21143,10 +21423,10 @@
       <c r="B28" s="35">
         <v>8</v>
       </c>
-      <c r="C28" s="258" t="s">
+      <c r="C28" s="259" t="s">
         <v>111</v>
       </c>
-      <c r="D28" s="258"/>
+      <c r="D28" s="259"/>
       <c r="E28" t="s">
         <v>124</v>
       </c>
@@ -21161,10 +21441,10 @@
       <c r="B30" s="36">
         <v>1</v>
       </c>
-      <c r="C30" s="260" t="s">
+      <c r="C30" s="258" t="s">
         <v>112</v>
       </c>
-      <c r="D30" s="260"/>
+      <c r="D30" s="258"/>
       <c r="E30" t="s">
         <v>107</v>
       </c>
@@ -21173,10 +21453,10 @@
       <c r="B31" s="36">
         <v>2</v>
       </c>
-      <c r="C31" s="260" t="s">
+      <c r="C31" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="D31" s="260"/>
+      <c r="D31" s="258"/>
       <c r="E31" t="s">
         <v>120</v>
       </c>
@@ -21185,10 +21465,10 @@
       <c r="B32" s="36">
         <v>3</v>
       </c>
-      <c r="C32" s="260" t="s">
+      <c r="C32" s="258" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="260"/>
+      <c r="D32" s="258"/>
       <c r="E32" t="s">
         <v>121</v>
       </c>
@@ -21200,10 +21480,10 @@
       <c r="B33" s="36">
         <v>4</v>
       </c>
-      <c r="C33" s="260" t="s">
+      <c r="C33" s="258" t="s">
         <v>115</v>
       </c>
-      <c r="D33" s="260"/>
+      <c r="D33" s="258"/>
       <c r="E33" t="s">
         <v>307</v>
       </c>
@@ -21212,10 +21492,10 @@
       <c r="B34" s="36">
         <v>5</v>
       </c>
-      <c r="C34" s="260" t="s">
+      <c r="C34" s="258" t="s">
         <v>122</v>
       </c>
-      <c r="D34" s="260"/>
+      <c r="D34" s="258"/>
       <c r="E34" t="s">
         <v>127</v>
       </c>
@@ -21237,10 +21517,10 @@
       <c r="B35" s="36">
         <v>6</v>
       </c>
-      <c r="C35" s="260" t="s">
+      <c r="C35" s="258" t="s">
         <v>123</v>
       </c>
-      <c r="D35" s="260"/>
+      <c r="D35" s="258"/>
       <c r="E35" t="s">
         <v>501</v>
       </c>
@@ -21249,10 +21529,10 @@
       <c r="B36" s="36">
         <v>7</v>
       </c>
-      <c r="C36" s="260" t="s">
+      <c r="C36" s="258" t="s">
         <v>125</v>
       </c>
-      <c r="D36" s="260"/>
+      <c r="D36" s="258"/>
       <c r="E36" t="s">
         <v>126</v>
       </c>
@@ -21261,10 +21541,10 @@
       <c r="B37" s="36">
         <v>8</v>
       </c>
-      <c r="C37" s="260" t="s">
+      <c r="C37" s="258" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="260"/>
+      <c r="D37" s="258"/>
       <c r="E37" t="s">
         <v>128</v>
       </c>
@@ -21284,10 +21564,10 @@
       <c r="B40" s="43">
         <v>1</v>
       </c>
-      <c r="C40" s="249" t="s">
+      <c r="C40" s="166" t="s">
         <v>310</v>
       </c>
-      <c r="D40" s="249"/>
+      <c r="D40" s="166"/>
       <c r="E40" t="s">
         <v>313</v>
       </c>
@@ -21308,10 +21588,10 @@
       <c r="B41" s="43">
         <v>2</v>
       </c>
-      <c r="C41" s="249" t="s">
+      <c r="C41" s="166" t="s">
         <v>402</v>
       </c>
-      <c r="D41" s="249"/>
+      <c r="D41" s="166"/>
       <c r="E41" t="s">
         <v>311</v>
       </c>
@@ -21337,10 +21617,10 @@
       <c r="B42" s="43">
         <v>3</v>
       </c>
-      <c r="C42" s="249" t="s">
+      <c r="C42" s="166" t="s">
         <v>401</v>
       </c>
-      <c r="D42" s="249"/>
+      <c r="D42" s="166"/>
       <c r="E42" t="s">
         <v>312</v>
       </c>
@@ -21360,10 +21640,10 @@
       <c r="B43" s="43">
         <v>4</v>
       </c>
-      <c r="C43" s="249" t="s">
+      <c r="C43" s="166" t="s">
         <v>400</v>
       </c>
-      <c r="D43" s="249"/>
+      <c r="D43" s="166"/>
       <c r="E43" t="s">
         <v>403</v>
       </c>
@@ -21384,10 +21664,10 @@
       <c r="B44" s="43">
         <v>5</v>
       </c>
-      <c r="C44" s="249" t="s">
+      <c r="C44" s="166" t="s">
         <v>314</v>
       </c>
-      <c r="D44" s="249"/>
+      <c r="D44" s="166"/>
       <c r="E44" t="s">
         <v>377</v>
       </c>
@@ -21408,10 +21688,10 @@
       <c r="B45" s="43">
         <v>6</v>
       </c>
-      <c r="C45" s="249" t="s">
+      <c r="C45" s="166" t="s">
         <v>315</v>
       </c>
-      <c r="D45" s="249"/>
+      <c r="D45" s="166"/>
       <c r="E45" t="s">
         <v>316</v>
       </c>
@@ -21429,10 +21709,10 @@
       <c r="B46" s="43">
         <v>7</v>
       </c>
-      <c r="C46" s="249" t="s">
+      <c r="C46" s="166" t="s">
         <v>318</v>
       </c>
-      <c r="D46" s="249"/>
+      <c r="D46" s="166"/>
       <c r="E46" t="s">
         <v>319</v>
       </c>
@@ -21456,10 +21736,10 @@
       <c r="B47" s="43">
         <v>8</v>
       </c>
-      <c r="C47" s="249" t="s">
+      <c r="C47" s="166" t="s">
         <v>171</v>
       </c>
-      <c r="D47" s="249"/>
+      <c r="D47" s="166"/>
       <c r="E47" t="s">
         <v>317</v>
       </c>
@@ -21495,16 +21775,24 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C24:D24"/>
@@ -21517,24 +21805,16 @@
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
